--- a/data/trans_orig/AIRE_1-Edad-trans_orig.xlsx
+++ b/data/trans_orig/AIRE_1-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según lo que estarían dispuestos a pagar al año para que la administración pública ponga en marcha actuaciones (+++) en su municipio/ciudad (o lugar de residencia) que haga reducir la contaminación del aire en 2023</t>
+          <t>Población según lo que estarían dispuestos a pagar al año para que la administración pública ponga en marcha actuaciones (+++) en su municipio/ciudad (o lugar de residencia) que haga reducir la contaminación del aire en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4431</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13854</t>
+          <t>11941</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13778</t>
+          <t>13756</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21364</t>
+          <t>19114</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>803</t>
+          <t>968</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>20913</t>
+          <t>19549</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,67%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4431</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2899</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>3594</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4431</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2899</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3594</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4431</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2899</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3594</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4431</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2899</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>3594</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1380,12 +1380,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1408,12 +1408,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4431</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6548</t>
+          <t>5683</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7374</t>
+          <t>6859</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -1521,12 +1521,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>177</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30825</t>
+          <t>29397</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1556,12 +1556,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2528</t>
+          <t>2293</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21665</t>
+          <t>21776</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1571,12 +1571,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6625</t>
+          <t>7347</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>37550</t>
+          <t>38873</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1606,12 +1606,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>11,28%</t>
         </is>
       </c>
     </row>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14804</t>
+          <t>15981</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10129</t>
+          <t>10296</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1159</t>
+          <t>1111</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>16930</t>
+          <t>14634</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1719,12 +1719,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -1747,12 +1747,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12517</t>
+          <t>13961</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>52497</t>
+          <t>54257</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1782,12 +1782,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>1328</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15976</t>
+          <t>16542</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1817,12 +1817,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17442</t>
+          <t>17055</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>59858</t>
+          <t>60590</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,58%</t>
         </is>
       </c>
     </row>
@@ -1860,12 +1860,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10028</t>
+          <t>9163</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>33167</t>
+          <t>32197</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1895,12 +1895,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17711</t>
+          <t>18044</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>42448</t>
+          <t>42835</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1930,12 +1930,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>32096</t>
+          <t>32433</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>65907</t>
+          <t>67287</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,52%</t>
         </is>
       </c>
     </row>
@@ -1973,12 +1973,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>99217</t>
+          <t>98703</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>145143</t>
+          <t>145082</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1988,12 +1988,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>52,95%</t>
+          <t>52,68%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>77,43%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2008,12 +2008,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>93033</t>
+          <t>92649</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>124597</t>
+          <t>123267</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2023,12 +2023,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>59,14%</t>
+          <t>58,9%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>78,37%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2043,12 +2043,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>204758</t>
+          <t>201298</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>259752</t>
+          <t>257853</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2058,12 +2058,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>59,41%</t>
+          <t>58,4%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>74,81%</t>
         </is>
       </c>
     </row>
@@ -2203,12 +2203,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2654</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2218,12 +2218,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7351</t>
+          <t>6848</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>8303</t>
+          <t>6846</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9480</t>
+          <t>9687</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10938</t>
+          <t>10502</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1681</t>
+          <t>1668</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>13393</t>
+          <t>13720</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2401,12 +2401,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -2429,12 +2429,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2654</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2444,12 +2444,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1809</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2479,12 +2479,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2147</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2514,12 +2514,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10878</t>
+          <t>9750</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2612,12 +2612,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>163</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>9433</t>
+          <t>8693</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -2655,12 +2655,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2654</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2670,12 +2670,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5298</t>
+          <t>5428</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>5769</t>
+          <t>5363</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9142</t>
+          <t>9151</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9070</t>
+          <t>9114</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>970</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>11880</t>
+          <t>11559</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -2886,7 +2886,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>11091</t>
+          <t>8614</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5551</t>
+          <t>6279</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>9112</t>
+          <t>9441</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -2994,12 +2994,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1621</t>
+          <t>1550</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>18550</t>
+          <t>17601</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3009,12 +3009,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1114</t>
+          <t>1236</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>14384</t>
+          <t>15016</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4248</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>22777</t>
+          <t>24240</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,3%</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>13198</t>
+          <t>13914</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3127,7 +3127,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3142,12 +3142,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>986</t>
+          <t>939</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9147</t>
+          <t>8291</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1799</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>17275</t>
+          <t>17084</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -3220,12 +3220,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>9558</t>
+          <t>9951</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>32343</t>
+          <t>32294</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3235,12 +3235,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3268</t>
+          <t>3456</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>14454</t>
+          <t>14955</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>16030</t>
+          <t>16081</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>41699</t>
+          <t>41931</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,9%</t>
         </is>
       </c>
     </row>
@@ -3333,12 +3333,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>14797</t>
+          <t>15042</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>35846</t>
+          <t>35693</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3348,12 +3348,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>13405</t>
+          <t>13938</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>30657</t>
+          <t>31632</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>33137</t>
+          <t>32077</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>58872</t>
+          <t>59473</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,45%</t>
         </is>
       </c>
     </row>
@@ -3446,12 +3446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>112131</t>
+          <t>111747</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>144644</t>
+          <t>144042</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3461,12 +3461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>60,02%</t>
+          <t>59,81%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>77,1%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>133092</t>
+          <t>136647</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>160705</t>
+          <t>160752</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>67,22%</t>
+          <t>69,01%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>81,19%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>257783</t>
+          <t>254655</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>297660</t>
+          <t>298205</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>66,99%</t>
+          <t>66,18%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>77,49%</t>
         </is>
       </c>
     </row>
@@ -3676,12 +3676,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2071</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>14775</t>
+          <t>13425</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3691,12 +3691,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3711,12 +3711,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>159</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5633</t>
+          <t>5454</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3748</t>
+          <t>3961</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>16854</t>
+          <t>16112</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -3789,12 +3789,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>867</t>
+          <t>899</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>9543</t>
+          <t>10457</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3804,12 +3804,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1596</t>
+          <t>1463</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>8097</t>
+          <t>7989</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3839,47 +3839,47 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>3,1%</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>7273</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>3427</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>14499</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
           <t>0,62%</t>
         </is>
       </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>3,15%</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>7273</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t>3488</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="inlineStr">
-        <is>
-          <t>14013</t>
-        </is>
-      </c>
-      <c r="U31" s="2" t="inlineStr">
-        <is>
-          <t>1,32%</t>
-        </is>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -3902,12 +3902,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1896</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3917,12 +3917,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1202</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>5869</t>
+          <t>6994</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1202</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>6754</t>
+          <t>5909</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -4128,12 +4128,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1896</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4143,12 +4143,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4168,7 +4168,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>4607</t>
+          <t>4758</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>4536</t>
+          <t>5731</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -4241,12 +4241,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1156</t>
+          <t>1182</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>10075</t>
+          <t>11242</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4256,12 +4256,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4276,12 +4276,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>783</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>8322</t>
+          <t>7635</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4296,7 +4296,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4311,12 +4311,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>3319</t>
+          <t>3452</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>15815</t>
+          <t>13948</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -4359,7 +4359,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>7686</t>
+          <t>6902</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>697</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>6863</t>
+          <t>6245</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4404,47 +4404,47 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>2,43%</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>4572</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>1552</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>9910</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
           <t>0,28%</t>
         </is>
       </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>2,67%</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R36" s="2" t="inlineStr">
-        <is>
-          <t>4572</t>
-        </is>
-      </c>
-      <c r="S36" s="2" t="inlineStr">
-        <is>
-          <t>1544</t>
-        </is>
-      </c>
-      <c r="T36" s="2" t="inlineStr">
-        <is>
-          <t>10654</t>
-        </is>
-      </c>
-      <c r="U36" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="V36" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -4467,12 +4467,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1046</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>9594</t>
+          <t>10460</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>5661</t>
+          <t>5790</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>17704</t>
+          <t>17024</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4517,12 +4517,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>8891</t>
+          <t>8648</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>22911</t>
+          <t>22585</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4552,12 +4552,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,09%</t>
         </is>
       </c>
     </row>
@@ -4580,12 +4580,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>4181</t>
+          <t>3848</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>18147</t>
+          <t>18772</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>1936</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>8683</t>
+          <t>8786</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>7008</t>
+          <t>7482</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>23411</t>
+          <t>23231</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,2%</t>
         </is>
       </c>
     </row>
@@ -4693,12 +4693,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>10512</t>
+          <t>10624</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>29083</t>
+          <t>29138</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4708,12 +4708,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>12428</t>
+          <t>12295</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>26265</t>
+          <t>25985</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>26777</t>
+          <t>27121</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>49965</t>
+          <t>50498</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,14%</t>
         </is>
       </c>
     </row>
@@ -4806,12 +4806,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>25983</t>
+          <t>25919</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>49890</t>
+          <t>47398</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4821,12 +4821,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>20944</t>
+          <t>20959</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>36143</t>
+          <t>36760</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>52342</t>
+          <t>52082</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>79171</t>
+          <t>78297</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,17%</t>
         </is>
       </c>
     </row>
@@ -4919,12 +4919,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>192886</t>
+          <t>193609</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>226046</t>
+          <t>224916</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4934,12 +4934,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>65,3%</t>
+          <t>65,55%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>76,15%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>171570</t>
+          <t>172434</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>195416</t>
+          <t>195702</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4969,12 +4969,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>66,66%</t>
+          <t>67,0%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>76,04%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>371220</t>
+          <t>371161</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>411777</t>
+          <t>412270</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>67,16%</t>
+          <t>67,15%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>74,5%</t>
+          <t>74,59%</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>7282</t>
+          <t>8451</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>668</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>6266</t>
+          <t>6174</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5204,7 +5204,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1681</t>
+          <t>1631</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>10345</t>
+          <t>9462</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -5262,12 +5262,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1670</t>
+          <t>1117</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>12210</t>
+          <t>11166</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5277,12 +5277,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1438</t>
+          <t>1580</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>9261</t>
+          <t>9254</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5312,7 +5312,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>3970</t>
+          <t>4112</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>15732</t>
+          <t>15465</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -5375,12 +5375,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>1874</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5390,12 +5390,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5425,12 +5425,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5493,7 +5493,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>5496</t>
+          <t>5435</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>4106</t>
+          <t>3729</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5543,7 +5543,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>467</t>
+          <t>432</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>6946</t>
+          <t>6529</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -5601,12 +5601,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>1874</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5616,12 +5616,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>3257</t>
+          <t>3696</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5656,7 +5656,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>4163</t>
+          <t>3503</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5691,7 +5691,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,51%</t>
         </is>
       </c>
     </row>
@@ -5714,12 +5714,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>1098</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>11321</t>
+          <t>10538</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5729,12 +5729,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5749,12 +5749,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2191</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>10039</t>
+          <t>10137</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5764,12 +5764,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>4893</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>16758</t>
+          <t>17082</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5799,12 +5799,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -5832,7 +5832,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>6665</t>
+          <t>7064</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5847,7 +5847,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5867,7 +5867,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>4824</t>
+          <t>4891</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5882,7 +5882,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>984</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>8437</t>
+          <t>8710</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>3493</t>
+          <t>3422</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>17319</t>
+          <t>17026</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5975,12 +5975,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>7434</t>
+          <t>7919</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>137016</t>
+          <t>140910</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -5990,12 +5990,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>39,21%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6010,12 +6010,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>14696</t>
+          <t>15031</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>165853</t>
+          <t>152932</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6025,12 +6025,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>22,06%</t>
         </is>
       </c>
     </row>
@@ -6053,12 +6053,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>3800</t>
+          <t>3144</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>15945</t>
+          <t>14632</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>845</t>
+          <t>804</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>6564</t>
+          <t>6340</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6103,12 +6103,12 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6123,12 +6123,12 @@
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>5840</t>
+          <t>5490</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>18355</t>
+          <t>17793</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6138,12 +6138,12 @@
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -6166,12 +6166,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>4033</t>
+          <t>3809</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>16071</t>
+          <t>16094</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>11681</t>
+          <t>11845</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>25461</t>
+          <t>26430</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6216,12 +6216,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>19460</t>
+          <t>18788</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>37841</t>
+          <t>37006</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6251,12 +6251,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>35401</t>
+          <t>34788</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>60108</t>
+          <t>58867</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6314,12 +6314,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>23474</t>
+          <t>22545</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>42261</t>
+          <t>42071</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6329,12 +6329,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>62733</t>
+          <t>63317</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>95723</t>
+          <t>94554</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6364,12 +6364,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,64%</t>
         </is>
       </c>
     </row>
@@ -6392,12 +6392,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>231043</t>
+          <t>231789</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>264085</t>
+          <t>263864</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6407,12 +6407,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>69,43%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>79,04%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6427,12 +6427,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>173605</t>
+          <t>174498</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>279457</t>
+          <t>277998</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6442,12 +6442,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>48,56%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>77,36%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6462,12 +6462,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>412158</t>
+          <t>413132</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>530970</t>
+          <t>530923</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6477,12 +6477,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>59,46%</t>
+          <t>59,6%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>76,59%</t>
         </is>
       </c>
     </row>
@@ -6627,7 +6627,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>4845</t>
+          <t>4999</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6642,7 +6642,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6662,7 +6662,7 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>4628</t>
+          <t>4564</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6677,7 +6677,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6697,7 +6697,7 @@
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>6355</t>
+          <t>6327</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6712,7 +6712,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>1031</t>
+          <t>1174</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>10808</t>
+          <t>12881</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6775,7 +6775,7 @@
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>3994</t>
+          <t>4644</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6790,7 +6790,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6805,12 +6805,12 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>2325</t>
+          <t>2310</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>12356</t>
+          <t>12353</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -6820,7 +6820,7 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>1615</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -6863,12 +6863,12 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6888,7 +6888,7 @@
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>3329</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -6903,7 +6903,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6923,7 +6923,7 @@
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>3824</t>
+          <t>3291</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -6938,7 +6938,7 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -6966,7 +6966,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>985</t>
+          <t>826</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -6981,7 +6981,7 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -7001,7 +7001,7 @@
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>3789</t>
+          <t>2635</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>4323</t>
+          <t>3484</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -7051,7 +7051,7 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,58%</t>
         </is>
       </c>
     </row>
@@ -7074,12 +7074,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>1615</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7089,12 +7089,12 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -7114,7 +7114,7 @@
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>3343</t>
+          <t>3321</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7149,7 +7149,7 @@
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>4033</t>
+          <t>3271</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -7164,7 +7164,7 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,54%</t>
         </is>
       </c>
     </row>
@@ -7187,12 +7187,12 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>1007</t>
+          <t>1383</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>10680</t>
+          <t>10286</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7202,12 +7202,12 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>2441</t>
+          <t>2304</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>9240</t>
+          <t>9418</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7237,12 +7237,12 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7257,12 +7257,12 @@
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>4714</t>
+          <t>5068</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>16301</t>
+          <t>15665</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -7272,12 +7272,12 @@
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -7305,7 +7305,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>7373</t>
+          <t>9080</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7320,7 +7320,7 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -7335,12 +7335,12 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>636</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>5942</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7355,7 +7355,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7370,12 +7370,12 @@
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>1124</t>
+          <t>1256</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>8508</t>
+          <t>8938</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -7385,12 +7385,12 @@
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -7413,12 +7413,12 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>782</t>
+          <t>771</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>10014</t>
+          <t>9307</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -7448,12 +7448,12 @@
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>2945</t>
+          <t>2840</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>10482</t>
+          <t>9965</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7463,12 +7463,12 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7483,12 +7483,12 @@
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>5066</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>15148</t>
+          <t>16403</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -7498,12 +7498,12 @@
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -7526,12 +7526,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>2855</t>
+          <t>2943</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>14806</t>
+          <t>14122</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -7561,12 +7561,12 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>1696</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>8354</t>
+          <t>8422</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -7576,12 +7576,12 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>6758</t>
+          <t>6927</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>18935</t>
+          <t>19159</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -7611,12 +7611,12 @@
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -7639,12 +7639,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>7083</t>
+          <t>7067</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>22284</t>
+          <t>23092</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -7674,12 +7674,12 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>12384</t>
+          <t>12554</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>24252</t>
+          <t>24297</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>23101</t>
+          <t>23618</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>43085</t>
+          <t>42627</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -7724,12 +7724,12 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,09%</t>
         </is>
       </c>
     </row>
@@ -7752,12 +7752,12 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>22708</t>
+          <t>22950</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>41841</t>
+          <t>41409</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>24949</t>
+          <t>25074</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>40286</t>
+          <t>40265</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -7802,7 +7802,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>52166</t>
+          <t>52835</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>76041</t>
+          <t>76548</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
@@ -7837,12 +7837,12 @@
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,73%</t>
         </is>
       </c>
     </row>
@@ -7865,12 +7865,12 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>226606</t>
+          <t>227143</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>254916</t>
+          <t>253883</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>73,96%</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>83,01%</t>
+          <t>82,67%</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -7900,12 +7900,12 @@
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>210574</t>
+          <t>211105</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>233130</t>
+          <t>232498</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>71,58%</t>
+          <t>71,76%</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>79,04%</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>444961</t>
+          <t>445183</t>
         </is>
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>478181</t>
+          <t>479066</t>
         </is>
       </c>
       <c r="U67" s="2" t="inlineStr">
@@ -7950,12 +7950,12 @@
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>74,0%</t>
+          <t>74,04%</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>79,68%</t>
         </is>
       </c>
     </row>
@@ -8100,7 +8100,7 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>5142</t>
+          <t>4487</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -8135,7 +8135,7 @@
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>4795</t>
+          <t>4831</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8165,12 +8165,12 @@
       </c>
       <c r="S69" s="2" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>385</t>
         </is>
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
-          <t>7065</t>
+          <t>7191</t>
         </is>
       </c>
       <c r="U69" s="2" t="inlineStr">
@@ -8180,12 +8180,12 @@
       </c>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -8208,12 +8208,12 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>759</t>
+          <t>749</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>7438</t>
+          <t>7154</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -8248,7 +8248,7 @@
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>2459</t>
+          <t>2420</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="S70" s="2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>455</t>
         </is>
       </c>
       <c r="T70" s="2" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>7657</t>
         </is>
       </c>
       <c r="U70" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -8321,12 +8321,12 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
@@ -8356,12 +8356,12 @@
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>1848</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="S71" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T71" s="2" t="inlineStr">
         <is>
-          <t>1593</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U71" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8434,12 +8434,12 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -8469,12 +8469,12 @@
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>1848</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="S72" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>1593</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U72" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8547,12 +8547,12 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -8562,12 +8562,12 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -8582,12 +8582,12 @@
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>1848</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -8597,12 +8597,12 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -8617,12 +8617,12 @@
       </c>
       <c r="S73" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>1593</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U73" s="2" t="inlineStr">
@@ -8632,12 +8632,12 @@
       </c>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8660,12 +8660,12 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>756</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>6685</t>
+          <t>6729</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -8680,7 +8680,7 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -8695,12 +8695,12 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>5592</t>
+          <t>5346</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -8710,12 +8710,12 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -8730,12 +8730,12 @@
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>980</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>9332</t>
+          <t>9366</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
@@ -8745,7 +8745,7 @@
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
@@ -8778,7 +8778,7 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>6084</t>
+          <t>5262</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -8793,7 +8793,7 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
@@ -8813,7 +8813,7 @@
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>7764</t>
+          <t>7116</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -8828,7 +8828,7 @@
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -8843,12 +8843,12 @@
       </c>
       <c r="S75" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>881</t>
         </is>
       </c>
       <c r="T75" s="2" t="inlineStr">
         <is>
-          <t>9727</t>
+          <t>9813</t>
         </is>
       </c>
       <c r="U75" s="2" t="inlineStr">
@@ -8858,12 +8858,12 @@
       </c>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -8886,12 +8886,12 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>3289</t>
+          <t>3556</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>12199</t>
+          <t>13308</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -8901,12 +8901,12 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -8921,12 +8921,12 @@
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>1185</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>14715</t>
+          <t>14354</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -8936,12 +8936,12 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -8956,12 +8956,12 @@
       </c>
       <c r="S76" s="2" t="inlineStr">
         <is>
-          <t>3881</t>
+          <t>4481</t>
         </is>
       </c>
       <c r="T76" s="2" t="inlineStr">
         <is>
-          <t>22231</t>
+          <t>22567</t>
         </is>
       </c>
       <c r="U76" s="2" t="inlineStr">
@@ -8971,12 +8971,12 @@
       </c>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -8999,12 +8999,12 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>1485</t>
+          <t>1506</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>8496</t>
+          <t>8441</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -9014,12 +9014,12 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
@@ -9034,12 +9034,12 @@
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>319</t>
+          <t>214</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>7229</t>
+          <t>7286</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -9049,12 +9049,12 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9069,12 +9069,12 @@
       </c>
       <c r="S77" s="2" t="inlineStr">
         <is>
-          <t>1865</t>
+          <t>1761</t>
         </is>
       </c>
       <c r="T77" s="2" t="inlineStr">
         <is>
-          <t>13174</t>
+          <t>13115</t>
         </is>
       </c>
       <c r="U77" s="2" t="inlineStr">
@@ -9084,12 +9084,12 @@
       </c>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -9112,12 +9112,12 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>3853</t>
+          <t>4298</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>13065</t>
+          <t>13247</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
@@ -9147,12 +9147,12 @@
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>1219</t>
+          <t>1371</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>14056</t>
+          <t>14634</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -9182,12 +9182,12 @@
       </c>
       <c r="S78" s="2" t="inlineStr">
         <is>
-          <t>3323</t>
+          <t>4362</t>
         </is>
       </c>
       <c r="T78" s="2" t="inlineStr">
         <is>
-          <t>24256</t>
+          <t>23829</t>
         </is>
       </c>
       <c r="U78" s="2" t="inlineStr">
@@ -9197,12 +9197,12 @@
       </c>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -9225,12 +9225,12 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>13223</t>
+          <t>13345</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>25813</t>
+          <t>25238</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
@@ -9260,12 +9260,12 @@
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>4568</t>
+          <t>3972</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>35780</t>
+          <t>35804</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -9295,12 +9295,12 @@
       </c>
       <c r="S79" s="2" t="inlineStr">
         <is>
-          <t>12507</t>
+          <t>12871</t>
         </is>
       </c>
       <c r="T79" s="2" t="inlineStr">
         <is>
-          <t>56790</t>
+          <t>57536</t>
         </is>
       </c>
       <c r="U79" s="2" t="inlineStr">
@@ -9310,12 +9310,12 @@
       </c>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,59%</t>
         </is>
       </c>
     </row>
@@ -9338,12 +9338,12 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>138683</t>
+          <t>139201</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>157889</t>
+          <t>158055</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -9353,12 +9353,12 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>71,56%</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -9373,12 +9373,12 @@
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>325484</t>
+          <t>326013</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>394333</t>
+          <t>394750</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -9388,12 +9388,12 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -9408,12 +9408,12 @@
       </c>
       <c r="S80" s="2" t="inlineStr">
         <is>
-          <t>468488</t>
+          <t>468985</t>
         </is>
       </c>
       <c r="T80" s="2" t="inlineStr">
         <is>
-          <t>573994</t>
+          <t>569161</t>
         </is>
       </c>
       <c r="U80" s="2" t="inlineStr">
@@ -9423,12 +9423,12 @@
       </c>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>78,2%</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>94,9%</t>
         </is>
       </c>
     </row>
@@ -9573,7 +9573,7 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>3120</t>
+          <t>3159</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -9588,7 +9588,7 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -9608,7 +9608,7 @@
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>2925</t>
+          <t>2934</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -9643,7 +9643,7 @@
       </c>
       <c r="T82" s="2" t="inlineStr">
         <is>
-          <t>4541</t>
+          <t>4233</t>
         </is>
       </c>
       <c r="U82" s="2" t="inlineStr">
@@ -9658,7 +9658,7 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -9681,12 +9681,12 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>695</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>6359</t>
+          <t>6073</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -9696,12 +9696,12 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
@@ -9716,12 +9716,12 @@
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>384</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>4670</t>
+          <t>4665</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -9736,7 +9736,7 @@
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -9751,12 +9751,12 @@
       </c>
       <c r="S83" s="2" t="inlineStr">
         <is>
-          <t>1434</t>
+          <t>1415</t>
         </is>
       </c>
       <c r="T83" s="2" t="inlineStr">
         <is>
-          <t>8102</t>
+          <t>8447</t>
         </is>
       </c>
       <c r="U83" s="2" t="inlineStr">
@@ -9771,7 +9771,7 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -9794,12 +9794,12 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>1175</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -9809,12 +9809,12 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -9829,12 +9829,12 @@
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -9844,12 +9844,12 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -9864,12 +9864,12 @@
       </c>
       <c r="S84" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T84" s="2" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U84" s="2" t="inlineStr">
@@ -9879,12 +9879,12 @@
       </c>
       <c r="V84" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9907,12 +9907,12 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>1175</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -9922,12 +9922,12 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
@@ -9942,12 +9942,12 @@
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -9957,12 +9957,12 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -9977,12 +9977,12 @@
       </c>
       <c r="S85" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T85" s="2" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U85" s="2" t="inlineStr">
@@ -9992,12 +9992,12 @@
       </c>
       <c r="V85" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10020,12 +10020,12 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>1175</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -10035,12 +10035,12 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
@@ -10055,12 +10055,12 @@
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -10070,12 +10070,12 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -10090,12 +10090,12 @@
       </c>
       <c r="S86" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T86" s="2" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U86" s="2" t="inlineStr">
@@ -10105,12 +10105,12 @@
       </c>
       <c r="V86" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10138,7 +10138,7 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>5131</t>
+          <t>4704</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -10153,7 +10153,7 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
@@ -10173,7 +10173,7 @@
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>3860</t>
+          <t>3963</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -10188,7 +10188,7 @@
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
@@ -10203,12 +10203,12 @@
       </c>
       <c r="S87" s="2" t="inlineStr">
         <is>
-          <t>1156</t>
+          <t>992</t>
         </is>
       </c>
       <c r="T87" s="2" t="inlineStr">
         <is>
-          <t>6711</t>
+          <t>6475</t>
         </is>
       </c>
       <c r="U87" s="2" t="inlineStr">
@@ -10218,12 +10218,12 @@
       </c>
       <c r="V87" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -10251,7 +10251,7 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>5640</t>
+          <t>5071</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -10266,7 +10266,7 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
@@ -10286,7 +10286,7 @@
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>3555</t>
+          <t>4001</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -10301,7 +10301,7 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -10316,12 +10316,12 @@
       </c>
       <c r="S88" s="2" t="inlineStr">
         <is>
-          <t>807</t>
+          <t>813</t>
         </is>
       </c>
       <c r="T88" s="2" t="inlineStr">
         <is>
-          <t>6541</t>
+          <t>6883</t>
         </is>
       </c>
       <c r="U88" s="2" t="inlineStr">
@@ -10336,7 +10336,7 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -10359,12 +10359,12 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>1506</t>
+          <t>1551</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>8456</t>
+          <t>8895</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
@@ -10394,12 +10394,12 @@
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>332</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>3018</t>
+          <t>3497</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -10414,7 +10414,7 @@
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
@@ -10429,12 +10429,12 @@
       </c>
       <c r="S89" s="2" t="inlineStr">
         <is>
-          <t>2453</t>
+          <t>2258</t>
         </is>
       </c>
       <c r="T89" s="2" t="inlineStr">
         <is>
-          <t>10031</t>
+          <t>9463</t>
         </is>
       </c>
       <c r="U89" s="2" t="inlineStr">
@@ -10444,12 +10444,12 @@
       </c>
       <c r="V89" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -10472,12 +10472,12 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>631</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>5848</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -10492,7 +10492,7 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
@@ -10512,7 +10512,7 @@
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>846</t>
+          <t>896</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -10527,7 +10527,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -10542,12 +10542,12 @@
       </c>
       <c r="S90" s="2" t="inlineStr">
         <is>
-          <t>816</t>
+          <t>677</t>
         </is>
       </c>
       <c r="T90" s="2" t="inlineStr">
         <is>
-          <t>6005</t>
+          <t>6546</t>
         </is>
       </c>
       <c r="U90" s="2" t="inlineStr">
@@ -10557,12 +10557,12 @@
       </c>
       <c r="V90" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -10585,12 +10585,12 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>2434</t>
+          <t>2487</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>9818</t>
+          <t>9698</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
@@ -10620,12 +10620,12 @@
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>3869</t>
+          <t>4033</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>10870</t>
+          <t>10681</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -10635,12 +10635,12 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -10655,12 +10655,12 @@
       </c>
       <c r="S91" s="2" t="inlineStr">
         <is>
-          <t>8130</t>
+          <t>7726</t>
         </is>
       </c>
       <c r="T91" s="2" t="inlineStr">
         <is>
-          <t>17699</t>
+          <t>17395</t>
         </is>
       </c>
       <c r="U91" s="2" t="inlineStr">
@@ -10670,12 +10670,12 @@
       </c>
       <c r="V91" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -10698,12 +10698,12 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>10365</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>21129</t>
+          <t>22002</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -10713,12 +10713,12 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
@@ -10733,12 +10733,12 @@
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>15323</t>
+          <t>15298</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>27108</t>
+          <t>26752</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -10768,12 +10768,12 @@
       </c>
       <c r="S92" s="2" t="inlineStr">
         <is>
-          <t>28346</t>
+          <t>28850</t>
         </is>
       </c>
       <c r="T92" s="2" t="inlineStr">
         <is>
-          <t>43901</t>
+          <t>44427</t>
         </is>
       </c>
       <c r="U92" s="2" t="inlineStr">
@@ -10783,12 +10783,12 @@
       </c>
       <c r="V92" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,5%</t>
         </is>
       </c>
     </row>
@@ -10811,12 +10811,12 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>108969</t>
+          <t>108570</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>124347</t>
+          <t>125108</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -10826,12 +10826,12 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>72,37%</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
@@ -10846,12 +10846,12 @@
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>195017</t>
+          <t>195584</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>209616</t>
+          <t>209893</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -10861,12 +10861,12 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>82,49%</t>
+          <t>82,73%</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -10881,12 +10881,12 @@
       </c>
       <c r="S93" s="2" t="inlineStr">
         <is>
-          <t>307690</t>
+          <t>309123</t>
         </is>
       </c>
       <c r="T93" s="2" t="inlineStr">
         <is>
-          <t>330240</t>
+          <t>330621</t>
         </is>
       </c>
       <c r="U93" s="2" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="V93" s="2" t="inlineStr">
         <is>
-          <t>79,62%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,56%</t>
         </is>
       </c>
     </row>
@@ -11041,12 +11041,12 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>6034</t>
+          <t>5700</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>21226</t>
+          <t>20482</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
@@ -11076,12 +11076,12 @@
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>6163</t>
+          <t>5623</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>22457</t>
+          <t>21812</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -11091,12 +11091,12 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -11111,12 +11111,12 @@
       </c>
       <c r="S95" s="2" t="inlineStr">
         <is>
-          <t>14142</t>
+          <t>14626</t>
         </is>
       </c>
       <c r="T95" s="2" t="inlineStr">
         <is>
-          <t>35654</t>
+          <t>34500</t>
         </is>
       </c>
       <c r="U95" s="2" t="inlineStr">
@@ -11126,12 +11126,12 @@
       </c>
       <c r="V95" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -11154,12 +11154,12 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>14496</t>
+          <t>14063</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>43730</t>
+          <t>39894</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
@@ -11189,12 +11189,12 @@
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>8593</t>
+          <t>8986</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>23016</t>
+          <t>23820</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="S96" s="2" t="inlineStr">
         <is>
-          <t>25885</t>
+          <t>26686</t>
         </is>
       </c>
       <c r="T96" s="2" t="inlineStr">
         <is>
-          <t>56925</t>
+          <t>60935</t>
         </is>
       </c>
       <c r="U96" s="2" t="inlineStr">
@@ -11239,12 +11239,12 @@
       </c>
       <c r="V96" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -11267,12 +11267,12 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>1802</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
@@ -11307,7 +11307,7 @@
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>3257</t>
+          <t>3025</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -11322,7 +11322,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -11342,7 +11342,7 @@
       </c>
       <c r="T97" s="2" t="inlineStr">
         <is>
-          <t>3500</t>
+          <t>3409</t>
         </is>
       </c>
       <c r="U97" s="2" t="inlineStr">
@@ -11380,12 +11380,12 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>480</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>8363</t>
+          <t>9393</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -11395,12 +11395,12 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,03%</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
@@ -11415,12 +11415,12 @@
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>1440</t>
+          <t>1194</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>11188</t>
+          <t>11269</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -11430,47 +11430,47 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
+          <t>0,06%</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R98" s="2" t="inlineStr">
+        <is>
+          <t>6958</t>
+        </is>
+      </c>
+      <c r="S98" s="2" t="inlineStr">
+        <is>
+          <t>2988</t>
+        </is>
+      </c>
+      <c r="T98" s="2" t="inlineStr">
+        <is>
+          <t>14177</t>
+        </is>
+      </c>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
           <t>0,08%</t>
         </is>
       </c>
-      <c r="P98" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="Q98" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R98" s="2" t="inlineStr">
-        <is>
-          <t>6958</t>
-        </is>
-      </c>
-      <c r="S98" s="2" t="inlineStr">
-        <is>
-          <t>2989</t>
-        </is>
-      </c>
-      <c r="T98" s="2" t="inlineStr">
-        <is>
-          <t>15528</t>
-        </is>
-      </c>
-      <c r="U98" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="V98" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,4%</t>
         </is>
       </c>
     </row>
@@ -11493,12 +11493,12 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>1802</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -11508,74 +11508,74 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>3950</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>1256</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>8808</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>0,07%</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R99" s="2" t="inlineStr">
+        <is>
+          <t>3950</t>
+        </is>
+      </c>
+      <c r="S99" s="2" t="inlineStr">
+        <is>
+          <t>1406</t>
+        </is>
+      </c>
+      <c r="T99" s="2" t="inlineStr">
+        <is>
+          <t>9455</t>
+        </is>
+      </c>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
           <t>0,11%</t>
         </is>
       </c>
-      <c r="J99" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K99" s="2" t="inlineStr">
-        <is>
-          <t>3950</t>
-        </is>
-      </c>
-      <c r="L99" s="2" t="inlineStr">
-        <is>
-          <t>1363</t>
-        </is>
-      </c>
-      <c r="M99" s="2" t="inlineStr">
-        <is>
-          <t>9435</t>
-        </is>
-      </c>
-      <c r="N99" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="O99" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
-        </is>
-      </c>
-      <c r="P99" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="Q99" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R99" s="2" t="inlineStr">
-        <is>
-          <t>3950</t>
-        </is>
-      </c>
-      <c r="S99" s="2" t="inlineStr">
-        <is>
-          <t>1382</t>
-        </is>
-      </c>
-      <c r="T99" s="2" t="inlineStr">
-        <is>
-          <t>9165</t>
-        </is>
-      </c>
-      <c r="U99" s="2" t="inlineStr">
-        <is>
-          <t>0,11%</t>
-        </is>
-      </c>
       <c r="V99" s="2" t="inlineStr">
         <is>
           <t>0,04%</t>
@@ -11583,7 +11583,7 @@
       </c>
       <c r="W99" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
     </row>
@@ -11606,12 +11606,12 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>11206</t>
+          <t>11562</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>29953</t>
+          <t>30913</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -11621,12 +11621,12 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
@@ -11641,12 +11641,12 @@
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>11917</t>
+          <t>12209</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>27237</t>
+          <t>27779</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -11656,12 +11656,12 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr">
@@ -11676,12 +11676,12 @@
       </c>
       <c r="S100" s="2" t="inlineStr">
         <is>
-          <t>26620</t>
+          <t>26150</t>
         </is>
       </c>
       <c r="T100" s="2" t="inlineStr">
         <is>
-          <t>49676</t>
+          <t>50470</t>
         </is>
       </c>
       <c r="U100" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="V100" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -11719,12 +11719,12 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>5163</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>18756</t>
+          <t>18808</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -11734,12 +11734,12 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
@@ -11754,12 +11754,12 @@
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>7218</t>
+          <t>7078</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>19814</t>
+          <t>19382</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -11769,12 +11769,12 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr">
@@ -11789,12 +11789,12 @@
       </c>
       <c r="S101" s="2" t="inlineStr">
         <is>
-          <t>14509</t>
+          <t>14534</t>
         </is>
       </c>
       <c r="T101" s="2" t="inlineStr">
         <is>
-          <t>33567</t>
+          <t>33329</t>
         </is>
       </c>
       <c r="U101" s="2" t="inlineStr">
@@ -11832,12 +11832,12 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>28884</t>
+          <t>27483</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>65897</t>
+          <t>66248</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
@@ -11847,12 +11847,12 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
@@ -11867,12 +11867,12 @@
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>39635</t>
+          <t>39148</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>218708</t>
+          <t>193213</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -11882,12 +11882,12 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr">
@@ -11902,12 +11902,12 @@
       </c>
       <c r="S102" s="2" t="inlineStr">
         <is>
-          <t>80025</t>
+          <t>79237</t>
         </is>
       </c>
       <c r="T102" s="2" t="inlineStr">
         <is>
-          <t>239294</t>
+          <t>258990</t>
         </is>
       </c>
       <c r="U102" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="V102" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W102" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>7,27%</t>
         </is>
       </c>
     </row>
@@ -11945,12 +11945,12 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>25698</t>
+          <t>25010</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>52450</t>
+          <t>52351</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -11960,12 +11960,12 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
@@ -11980,12 +11980,12 @@
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>11824</t>
+          <t>11516</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>27949</t>
+          <t>28036</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -12015,12 +12015,12 @@
       </c>
       <c r="S103" s="2" t="inlineStr">
         <is>
-          <t>40723</t>
+          <t>41144</t>
         </is>
       </c>
       <c r="T103" s="2" t="inlineStr">
         <is>
-          <t>73581</t>
+          <t>72978</t>
         </is>
       </c>
       <c r="U103" s="2" t="inlineStr">
@@ -12030,12 +12030,12 @@
       </c>
       <c r="V103" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W103" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -12058,12 +12058,12 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>78520</t>
+          <t>77744</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>134861</t>
+          <t>131878</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -12073,12 +12073,12 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
@@ -12093,12 +12093,12 @@
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>56000</t>
+          <t>57592</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>99422</t>
+          <t>99232</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
@@ -12108,12 +12108,12 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
@@ -12128,12 +12128,12 @@
       </c>
       <c r="S104" s="2" t="inlineStr">
         <is>
-          <t>146865</t>
+          <t>142242</t>
         </is>
       </c>
       <c r="T104" s="2" t="inlineStr">
         <is>
-          <t>217481</t>
+          <t>220409</t>
         </is>
       </c>
       <c r="U104" s="2" t="inlineStr">
@@ -12143,12 +12143,12 @@
       </c>
       <c r="V104" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W104" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,19%</t>
         </is>
       </c>
     </row>
@@ -12171,12 +12171,12 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>165292</t>
+          <t>166850</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>215195</t>
+          <t>218082</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -12186,12 +12186,12 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
@@ -12206,12 +12206,12 @@
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>122740</t>
+          <t>122472</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>210604</t>
+          <t>209894</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
@@ -12221,12 +12221,12 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="Q105" s="2" t="inlineStr">
@@ -12241,12 +12241,12 @@
       </c>
       <c r="S105" s="2" t="inlineStr">
         <is>
-          <t>300038</t>
+          <t>300886</t>
         </is>
       </c>
       <c r="T105" s="2" t="inlineStr">
         <is>
-          <t>410084</t>
+          <t>410475</t>
         </is>
       </c>
       <c r="U105" s="2" t="inlineStr">
@@ -12256,12 +12256,12 @@
       </c>
       <c r="V105" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="W105" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,52%</t>
         </is>
       </c>
     </row>
@@ -12284,12 +12284,12 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>1173195</t>
+          <t>1172583</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>1257849</t>
+          <t>1257039</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
@@ -12299,12 +12299,12 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>70,89%</t>
+          <t>70,85%</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>75,95%</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
@@ -12319,12 +12319,12 @@
       </c>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>1404113</t>
+          <t>1405072</t>
         </is>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>1610666</t>
+          <t>1605310</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
@@ -12334,12 +12334,12 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>73,6%</t>
+          <t>73,65%</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>84,14%</t>
         </is>
       </c>
       <c r="Q106" s="2" t="inlineStr">
@@ -12354,12 +12354,12 @@
       </c>
       <c r="S106" s="2" t="inlineStr">
         <is>
-          <t>2613514</t>
+          <t>2615583</t>
         </is>
       </c>
       <c r="T106" s="2" t="inlineStr">
         <is>
-          <t>2857112</t>
+          <t>2854479</t>
         </is>
       </c>
       <c r="U106" s="2" t="inlineStr">
@@ -12369,12 +12369,12 @@
       </c>
       <c r="V106" s="2" t="inlineStr">
         <is>
-          <t>73,35%</t>
+          <t>73,41%</t>
         </is>
       </c>
       <c r="W106" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>80,12%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/AIRE_1-Edad-trans_orig.xlsx
+++ b/data/trans_orig/AIRE_1-Edad-trans_orig.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2592</t>
+          <t>2509</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11941</t>
+          <t>12616</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2592</t>
+          <t>2509</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13756</t>
+          <t>12697</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4210</t>
+          <t>3610</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19114</t>
+          <t>18323</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>1663</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>9575</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>4373</t>
+          <t>5273</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19549</t>
+          <t>22215</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>6,08%</t>
         </is>
       </c>
     </row>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>1242</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5683</t>
+          <t>6916</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>1242</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6859</t>
+          <t>6518</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -1516,32 +1516,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9125</t>
+          <t>10530</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>1863</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>29397</t>
+          <t>30739</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1551,32 +1551,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8431</t>
+          <t>8754</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2293</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21776</t>
+          <t>22745</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1586,32 +1586,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>17556</t>
+          <t>19284</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>7347</t>
+          <t>7684</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>38873</t>
+          <t>39672</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>10,86%</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3692</t>
+          <t>3840</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1639,12 +1639,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15981</t>
+          <t>14607</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1734</t>
+          <t>1707</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10296</t>
+          <t>8530</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1699,32 +1699,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>5426</t>
+          <t>5548</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1111</t>
+          <t>1188</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>14634</t>
+          <t>17254</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,72%</t>
         </is>
       </c>
     </row>
@@ -1742,32 +1742,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>28458</t>
+          <t>22111</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13961</t>
+          <t>11067</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>54257</t>
+          <t>42728</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1777,32 +1777,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5177</t>
+          <t>7581</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1328</t>
+          <t>2361</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16542</t>
+          <t>21111</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1812,32 +1812,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>33635</t>
+          <t>29692</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17055</t>
+          <t>15898</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>60590</t>
+          <t>50197</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>13,74%</t>
         </is>
       </c>
     </row>
@@ -1855,32 +1855,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>17958</t>
+          <t>16008</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9163</t>
+          <t>8533</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>32197</t>
+          <t>26880</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1890,32 +1890,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>29098</t>
+          <t>29396</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18044</t>
+          <t>19266</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>42835</t>
+          <t>46334</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1925,32 +1925,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>47056</t>
+          <t>45404</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>32433</t>
+          <t>31026</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>67287</t>
+          <t>61384</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>16,81%</t>
         </is>
       </c>
     </row>
@@ -1968,32 +1968,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>123927</t>
+          <t>127919</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>98703</t>
+          <t>106452</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>145082</t>
+          <t>145832</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>69,51%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>52,68%</t>
+          <t>57,85%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>77,43%</t>
+          <t>79,25%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2003,32 +2003,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>108808</t>
+          <t>128341</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>92649</t>
+          <t>111641</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>123267</t>
+          <t>143401</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>70,83%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>58,9%</t>
+          <t>61,61%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>78,37%</t>
+          <t>79,14%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2038,32 +2038,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>232735</t>
+          <t>256260</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>201298</t>
+          <t>228199</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>257853</t>
+          <t>282420</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>67,52%</t>
+          <t>70,17%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>58,4%</t>
+          <t>62,48%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>74,81%</t>
+          <t>77,33%</t>
         </is>
       </c>
     </row>
@@ -2081,17 +2081,17 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>187370</t>
+          <t>184018</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>187370</t>
+          <t>184018</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>187370</t>
+          <t>184018</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,17 +2116,17 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>157297</t>
+          <t>181193</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>157297</t>
+          <t>181193</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>157297</t>
+          <t>181193</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,17 +2151,17 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>344666</t>
+          <t>365212</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>344666</t>
+          <t>365212</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>344666</t>
+          <t>365212</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1341</t>
+          <t>1447</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6848</t>
+          <t>7308</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1341</t>
+          <t>1447</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6846</t>
+          <t>7341</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1706</t>
+          <t>3966</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2321,12 +2321,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9687</t>
+          <t>12872</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2346,32 +2346,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3635</t>
+          <t>3516</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>837</t>
+          <t>748</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10502</t>
+          <t>9834</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2381,32 +2381,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>5341</t>
+          <t>7482</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1668</t>
+          <t>2772</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>13720</t>
+          <t>18780</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -2537,7 +2537,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>1643</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2547,12 +2547,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>8125</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2625</t>
+          <t>2124</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9750</t>
+          <t>6868</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2607,32 +2607,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>2790</t>
+          <t>3767</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>928</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8693</t>
+          <t>10529</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>1086</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5428</t>
+          <t>5522</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>1086</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>5363</t>
+          <t>5872</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1814</t>
+          <t>2064</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2773,12 +2773,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9151</t>
+          <t>10653</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2547</t>
+          <t>2508</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9114</t>
+          <t>8282</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2833,32 +2833,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>4361</t>
+          <t>4572</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>970</t>
+          <t>879</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>11559</t>
+          <t>14338</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1563</t>
+          <t>1622</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2886,12 +2886,12 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>8614</t>
+          <t>8333</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1079</t>
+          <t>1067</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>6279</t>
+          <t>5343</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2642</t>
+          <t>2689</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
@@ -2956,12 +2956,12 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>9441</t>
+          <t>10471</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -2989,32 +2989,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>6384</t>
+          <t>7101</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1550</t>
+          <t>1463</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>17601</t>
+          <t>19840</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3024,32 +3024,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>5109</t>
+          <t>6407</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1236</t>
+          <t>1775</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>15016</t>
+          <t>16866</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3059,32 +3059,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>11494</t>
+          <t>13507</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>5756</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>24240</t>
+          <t>27488</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,25%</t>
         </is>
       </c>
     </row>
@@ -3102,7 +3102,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2765</t>
+          <t>2607</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -3112,12 +3112,12 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>13914</t>
+          <t>14587</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -3127,7 +3127,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3137,32 +3137,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>3180</t>
+          <t>3656</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>939</t>
+          <t>1068</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8291</t>
+          <t>8750</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3172,32 +3172,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>5945</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>17084</t>
+          <t>16193</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -3215,32 +3215,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>19067</t>
+          <t>23140</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>9951</t>
+          <t>12868</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>32294</t>
+          <t>40061</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3250,32 +3250,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>7609</t>
+          <t>10536</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3456</t>
+          <t>5712</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>14955</t>
+          <t>18882</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3285,32 +3285,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>26676</t>
+          <t>33676</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>16081</t>
+          <t>21271</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>41931</t>
+          <t>50402</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,46%</t>
         </is>
       </c>
     </row>
@@ -3328,32 +3328,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>24424</t>
+          <t>26959</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>15042</t>
+          <t>17219</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>35693</t>
+          <t>38428</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3363,32 +3363,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>20512</t>
+          <t>20274</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>13938</t>
+          <t>12714</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>31632</t>
+          <t>30717</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3398,32 +3398,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>44936</t>
+          <t>47233</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>32077</t>
+          <t>34928</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>59473</t>
+          <t>61667</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>14,02%</t>
         </is>
       </c>
     </row>
@@ -3441,102 +3441,102 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>128936</t>
+          <t>147057</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>111747</t>
+          <t>128867</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>144042</t>
+          <t>164028</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>69,01%</t>
+          <t>68,03%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>59,81%</t>
+          <t>59,62%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
+          <t>75,88%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>171194</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>156580</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>183115</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>76,49%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>69,96%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>81,82%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>318251</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>293545</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>339201</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>72,33%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>66,72%</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
           <t>77,1%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>149291</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>136647</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>160752</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>75,4%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>69,01%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>81,19%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>249</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>278226</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>254655</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>298205</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>72,3%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>66,18%</t>
-        </is>
-      </c>
-      <c r="W28" s="2" t="inlineStr">
-        <is>
-          <t>77,49%</t>
         </is>
       </c>
     </row>
@@ -3554,17 +3554,17 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>186824</t>
+          <t>216159</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>186824</t>
+          <t>216159</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>186824</t>
+          <t>216159</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,17 +3589,17 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>197996</t>
+          <t>223814</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>197996</t>
+          <t>223814</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>197996</t>
+          <t>223814</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3624,17 +3624,17 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>384820</t>
+          <t>439973</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>384820</t>
+          <t>439973</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>384820</t>
+          <t>439973</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3671,32 +3671,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>6540</t>
+          <t>7761</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>3075</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>13425</t>
+          <t>15715</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3706,32 +3706,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1706</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>696</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5454</t>
+          <t>7091</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3741,32 +3741,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>8246</t>
+          <t>10173</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3961</t>
+          <t>4431</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>16112</t>
+          <t>19455</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -3784,32 +3784,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>3491</t>
+          <t>3599</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>912</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>10457</t>
+          <t>9731</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3819,32 +3819,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>3783</t>
+          <t>4602</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1463</t>
+          <t>2207</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>7989</t>
+          <t>10004</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3854,32 +3854,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>7273</t>
+          <t>8201</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>3427</t>
+          <t>4063</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>14499</t>
+          <t>15062</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>1165</t>
+          <t>1118</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -4020,12 +4020,12 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>6994</t>
+          <t>5641</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4080,7 +4080,7 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1165</t>
+          <t>1118</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>5909</t>
+          <t>6286</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -4158,7 +4158,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>1490</t>
+          <t>1555</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -4168,12 +4168,12 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>4758</t>
+          <t>5456</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>1490</t>
+          <t>1555</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>5731</t>
+          <t>6141</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -4236,32 +4236,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>4160</t>
+          <t>4290</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1182</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>11242</t>
+          <t>10027</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4271,32 +4271,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>3240</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>783</t>
+          <t>817</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>7635</t>
+          <t>7663</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4306,32 +4306,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>7400</t>
+          <t>7566</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>3452</t>
+          <t>3232</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>13948</t>
+          <t>13986</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -4349,7 +4349,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>2281</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -4359,12 +4359,12 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>6902</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4384,32 +4384,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2292</t>
+          <t>2331</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>734</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>6245</t>
+          <t>6371</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4419,32 +4419,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>4572</t>
+          <t>4632</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1552</t>
+          <t>1594</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>9910</t>
+          <t>10888</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -4462,32 +4462,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>4172</t>
+          <t>3886</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1046</t>
+          <t>936</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>10460</t>
+          <t>8969</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4497,32 +4497,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>10597</t>
+          <t>12161</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>5790</t>
+          <t>7268</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>17024</t>
+          <t>20396</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4532,32 +4532,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>14768</t>
+          <t>16047</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>8648</t>
+          <t>10146</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>22585</t>
+          <t>24573</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -4575,22 +4575,22 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>9348</t>
+          <t>9472</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>3848</t>
+          <t>4400</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>18772</t>
+          <t>19171</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -4600,7 +4600,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4610,32 +4610,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>4346</t>
+          <t>4365</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1936</t>
+          <t>1431</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>8786</t>
+          <t>9142</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4645,32 +4645,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>13695</t>
+          <t>13837</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>7482</t>
+          <t>7562</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>23231</t>
+          <t>24029</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -4688,32 +4688,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>18228</t>
+          <t>23036</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>10624</t>
+          <t>15219</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>29138</t>
+          <t>36638</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4723,32 +4723,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>18512</t>
+          <t>20223</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>12295</t>
+          <t>12833</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>25985</t>
+          <t>28216</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4758,27 +4758,27 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>36740</t>
+          <t>43259</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>27121</t>
+          <t>31941</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>50498</t>
+          <t>57736</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -4801,32 +4801,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>36142</t>
+          <t>39879</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>25919</t>
+          <t>28801</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>47398</t>
+          <t>53363</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4836,32 +4836,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>27564</t>
+          <t>32877</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>20959</t>
+          <t>25162</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>36760</t>
+          <t>43028</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4871,32 +4871,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>63707</t>
+          <t>72756</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>52082</t>
+          <t>58376</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>78297</t>
+          <t>88631</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,03%</t>
         </is>
       </c>
     </row>
@@ -4914,32 +4914,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>209841</t>
+          <t>242534</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>193609</t>
+          <t>224191</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>224916</t>
+          <t>258555</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>71,04%</t>
+          <t>71,78%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>66,35%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>76,52%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4949,32 +4949,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>183849</t>
+          <t>210114</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>172434</t>
+          <t>196212</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>195702</t>
+          <t>222907</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>71,49%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>67,0%</t>
+          <t>66,76%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>76,04%</t>
+          <t>75,84%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4984,32 +4984,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>393690</t>
+          <t>452647</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>371161</t>
+          <t>429777</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>412270</t>
+          <t>475251</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>71,22%</t>
+          <t>71,65%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>68,03%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>75,22%</t>
         </is>
       </c>
     </row>
@@ -5027,17 +5027,17 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>295367</t>
+          <t>337875</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>295367</t>
+          <t>337875</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>295367</t>
+          <t>337875</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5062,17 +5062,17 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>257379</t>
+          <t>293917</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>257379</t>
+          <t>293917</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>257379</t>
+          <t>293917</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5097,17 +5097,17 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>552746</t>
+          <t>631791</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>552746</t>
+          <t>631791</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>552746</t>
+          <t>631791</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5144,7 +5144,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>2158</t>
+          <t>2286</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -5154,7 +5154,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>8451</t>
+          <t>7991</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5179,32 +5179,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>2567</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>707</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>6174</t>
+          <t>6176</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5214,32 +5214,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>4726</t>
+          <t>4891</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1631</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>9462</t>
+          <t>10753</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -5257,7 +5257,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>4623</t>
+          <t>4516</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -5267,22 +5267,22 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>11166</t>
+          <t>11935</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5292,32 +5292,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>4168</t>
+          <t>4183</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1580</t>
+          <t>1428</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>9254</t>
+          <t>8874</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5327,32 +5327,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>8792</t>
+          <t>8699</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>4112</t>
+          <t>4717</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>15465</t>
+          <t>16913</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>1189</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -5493,7 +5493,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>5435</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5518,7 +5518,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>1083</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -5528,12 +5528,12 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>3729</t>
+          <t>3939</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
@@ -5543,7 +5543,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5553,22 +5553,22 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>2210</t>
+          <t>2336</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>455</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>6529</t>
+          <t>6853</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
@@ -5578,7 +5578,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -5631,7 +5631,7 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>723</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>3696</t>
+          <t>4003</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5656,7 +5656,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>723</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
@@ -5676,12 +5676,12 @@
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>3503</t>
+          <t>4186</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
@@ -5691,7 +5691,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,59%</t>
         </is>
       </c>
     </row>
@@ -5709,22 +5709,22 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>4518</t>
+          <t>4716</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>1098</t>
+          <t>1144</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>10538</t>
+          <t>11990</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5744,32 +5744,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>5124</t>
+          <t>5255</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>2191</t>
+          <t>2387</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>10137</t>
+          <t>10004</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5779,32 +5779,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>9642</t>
+          <t>9972</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>4893</t>
+          <t>5045</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>17082</t>
+          <t>17257</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -5822,7 +5822,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>1974</t>
+          <t>1698</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -5832,12 +5832,12 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>7064</t>
+          <t>6022</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -5847,7 +5847,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5857,7 +5857,7 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>1463</t>
+          <t>1578</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>4891</t>
+          <t>5283</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
@@ -5882,7 +5882,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5892,32 +5892,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>3437</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>984</t>
+          <t>843</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>8710</t>
+          <t>7895</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -5935,32 +5935,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>8655</t>
+          <t>8925</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3349</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>17026</t>
+          <t>17734</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5970,32 +5970,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>41567</t>
+          <t>9881</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>7919</t>
+          <t>5606</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>140910</t>
+          <t>17111</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6005,32 +6005,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>50222</t>
+          <t>18806</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>15031</t>
+          <t>11767</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>152932</t>
+          <t>29514</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -6048,22 +6048,22 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>7780</t>
+          <t>7413</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>3144</t>
+          <t>3295</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>14632</t>
+          <t>14412</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6083,32 +6083,32 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>2626</t>
+          <t>3166</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>804</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>6340</t>
+          <t>6697</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6118,17 +6118,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>10405</t>
+          <t>10579</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>5490</t>
+          <t>5720</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>17793</t>
+          <t>17666</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6138,12 +6138,12 @@
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -6161,32 +6161,32 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>8357</t>
+          <t>9163</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>3809</t>
+          <t>4865</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>16094</t>
+          <t>16443</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6196,32 +6196,32 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>18232</t>
+          <t>19017</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>11845</t>
+          <t>13281</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>26430</t>
+          <t>26337</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6231,32 +6231,32 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>26588</t>
+          <t>28180</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>18788</t>
+          <t>20149</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>37006</t>
+          <t>38872</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -6274,32 +6274,32 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>46339</t>
+          <t>51398</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>34788</t>
+          <t>39077</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>58867</t>
+          <t>64230</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6309,32 +6309,32 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>32264</t>
+          <t>36031</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>22545</t>
+          <t>27662</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>42071</t>
+          <t>45001</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6344,32 +6344,32 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>78602</t>
+          <t>87429</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>63317</t>
+          <t>72791</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>94554</t>
+          <t>103777</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>14,71%</t>
         </is>
       </c>
     </row>
@@ -6387,32 +6387,32 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>248299</t>
+          <t>259991</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>231789</t>
+          <t>242987</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>263864</t>
+          <t>275398</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>74,38%</t>
+          <t>74,01%</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>69,17%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6422,32 +6422,32 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>249509</t>
+          <t>270421</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>174498</t>
+          <t>257687</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>277998</t>
+          <t>282814</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>69,44%</t>
+          <t>76,39%</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>72,79%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>77,36%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6457,32 +6457,32 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>497808</t>
+          <t>530412</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>413132</t>
+          <t>508268</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>530923</t>
+          <t>550461</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>71,82%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>59,6%</t>
+          <t>72,06%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>76,59%</t>
+          <t>78,05%</t>
         </is>
       </c>
     </row>
@@ -6500,17 +6500,17 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>333830</t>
+          <t>351294</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>333830</t>
+          <t>351294</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>333830</t>
+          <t>351294</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6535,17 +6535,17 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>359337</t>
+          <t>354008</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>359337</t>
+          <t>354008</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>359337</t>
+          <t>354008</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6570,17 +6570,17 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>693168</t>
+          <t>705302</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>693168</t>
+          <t>705302</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>693168</t>
+          <t>705302</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6617,7 +6617,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>859</t>
+          <t>945</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -6627,7 +6627,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>4999</t>
+          <t>4711</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6642,7 +6642,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6652,7 +6652,7 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>1384</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>4564</t>
+          <t>4821</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
@@ -6677,7 +6677,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6687,32 +6687,32 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>2178</t>
+          <t>2329</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>685</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>6327</t>
+          <t>6452</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -6730,32 +6730,32 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>4512</t>
+          <t>4510</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>1174</t>
+          <t>1134</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>12881</t>
+          <t>11742</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6765,7 +6765,7 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>1306</t>
+          <t>1377</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>4644</t>
+          <t>4854</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
@@ -6790,7 +6790,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6800,32 +6800,32 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>5818</t>
+          <t>5887</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>2310</t>
+          <t>2253</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>12353</t>
+          <t>12995</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -6878,7 +6878,7 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>715</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
@@ -6888,7 +6888,7 @@
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>3329</t>
+          <t>3582</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -6903,7 +6903,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6913,7 +6913,7 @@
       </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>715</t>
         </is>
       </c>
       <c r="S58" s="2" t="inlineStr">
@@ -6923,7 +6923,7 @@
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>3291</t>
+          <t>4166</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -6938,7 +6938,7 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -6956,7 +6956,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>5600</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -6981,7 +6981,7 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -6991,7 +6991,7 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>707</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
@@ -7001,12 +7001,12 @@
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>2635</t>
+          <t>3588</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7026,7 +7026,7 @@
       </c>
       <c r="R59" s="2" t="inlineStr">
         <is>
-          <t>793</t>
+          <t>1711</t>
         </is>
       </c>
       <c r="S59" s="2" t="inlineStr">
@@ -7036,12 +7036,12 @@
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>3484</t>
+          <t>5824</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="V59" s="2" t="inlineStr">
@@ -7051,7 +7051,7 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -7104,7 +7104,7 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>683</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
@@ -7114,12 +7114,12 @@
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>3321</t>
+          <t>4110</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7139,7 +7139,7 @@
       </c>
       <c r="R60" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>683</t>
         </is>
       </c>
       <c r="S60" s="2" t="inlineStr">
@@ -7149,12 +7149,12 @@
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>3271</t>
+          <t>3778</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="V60" s="2" t="inlineStr">
@@ -7164,7 +7164,7 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,57%</t>
         </is>
       </c>
     </row>
@@ -7182,32 +7182,32 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>4165</t>
+          <t>4278</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>1383</t>
+          <t>1007</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>10286</t>
+          <t>11935</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -7217,32 +7217,32 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>4793</t>
+          <t>5681</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>2304</t>
+          <t>2503</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>9418</t>
+          <t>10233</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7252,22 +7252,22 @@
       </c>
       <c r="R61" s="2" t="inlineStr">
         <is>
-          <t>8958</t>
+          <t>9959</t>
         </is>
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>5068</t>
+          <t>5529</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>15665</t>
+          <t>17033</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="V61" s="2" t="inlineStr">
@@ -7277,7 +7277,7 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -7295,7 +7295,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -7305,12 +7305,12 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>9080</t>
+          <t>8331</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -7320,7 +7320,7 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -7330,32 +7330,32 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>2432</t>
+          <t>2574</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>691</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>5942</t>
+          <t>6276</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7365,32 +7365,32 @@
       </c>
       <c r="R62" s="2" t="inlineStr">
         <is>
-          <t>3708</t>
+          <t>3861</t>
         </is>
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>1256</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>8938</t>
+          <t>8965</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -7408,67 +7408,67 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>3177</t>
+          <t>3041</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>717</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>9307</t>
+          <t>9036</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
+          <t>0,91%</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>2,71%</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>6741</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>3365</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>11994</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>2,07%</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
           <t>1,03%</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t>3,03%</t>
-        </is>
-      </c>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K63" s="2" t="inlineStr">
-        <is>
-          <t>5708</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="inlineStr">
-        <is>
-          <t>2840</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr">
-        <is>
-          <t>9965</t>
-        </is>
-      </c>
-      <c r="N63" s="2" t="inlineStr">
-        <is>
-          <t>1,94%</t>
-        </is>
-      </c>
-      <c r="O63" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7478,17 +7478,17 @@
       </c>
       <c r="R63" s="2" t="inlineStr">
         <is>
-          <t>8886</t>
+          <t>9781</t>
         </is>
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>5066</t>
+          <t>5474</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>16403</t>
+          <t>16845</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -7498,12 +7498,12 @@
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -7521,32 +7521,32 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>7030</t>
+          <t>7318</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>2943</t>
+          <t>2984</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>14122</t>
+          <t>15126</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -7556,32 +7556,32 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>4287</t>
+          <t>4887</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>8422</t>
+          <t>9221</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -7591,32 +7591,32 @@
       </c>
       <c r="R64" s="2" t="inlineStr">
         <is>
-          <t>11317</t>
+          <t>12205</t>
         </is>
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>6927</t>
+          <t>6517</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>19159</t>
+          <t>19835</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -7634,32 +7634,32 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>13803</t>
+          <t>15211</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>7067</t>
+          <t>8033</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>23092</t>
+          <t>25812</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -7669,32 +7669,32 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>18015</t>
+          <t>20758</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>12554</t>
+          <t>14583</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>24297</t>
+          <t>27860</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -7704,32 +7704,32 @@
       </c>
       <c r="R65" s="2" t="inlineStr">
         <is>
-          <t>31818</t>
+          <t>35969</t>
         </is>
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>23618</t>
+          <t>26155</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>42627</t>
+          <t>48373</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,34%</t>
         </is>
       </c>
     </row>
@@ -7747,32 +7747,32 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>31087</t>
+          <t>33384</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>22950</t>
+          <t>23870</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>41409</t>
+          <t>44406</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -7782,32 +7782,32 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>32226</t>
+          <t>35007</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>25074</t>
+          <t>27148</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>40265</t>
+          <t>43853</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -7817,32 +7817,32 @@
       </c>
       <c r="R66" s="2" t="inlineStr">
         <is>
-          <t>63313</t>
+          <t>68391</t>
         </is>
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>52835</t>
+          <t>55740</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>76548</t>
+          <t>81199</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,31%</t>
         </is>
       </c>
     </row>
@@ -7860,22 +7860,22 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>241027</t>
+          <t>262206</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>227143</t>
+          <t>246421</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>253883</t>
+          <t>277550</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>78,49%</t>
+          <t>78,7%</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -7885,7 +7885,7 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>83,3%</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -7895,32 +7895,32 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>222135</t>
+          <t>245729</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>211105</t>
+          <t>231364</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>232498</t>
+          <t>257449</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>75,32%</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>71,76%</t>
+          <t>70,92%</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>78,91%</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -7930,17 +7930,17 @@
       </c>
       <c r="R67" s="2" t="inlineStr">
         <is>
-          <t>463162</t>
+          <t>507935</t>
         </is>
       </c>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>445183</t>
+          <t>487757</t>
         </is>
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>479066</t>
+          <t>527702</t>
         </is>
       </c>
       <c r="U67" s="2" t="inlineStr">
@@ -7950,12 +7950,12 @@
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>74,04%</t>
+          <t>73,97%</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>79,68%</t>
+          <t>80,02%</t>
         </is>
       </c>
     </row>
@@ -7973,17 +7973,17 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>307098</t>
+          <t>333182</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>307098</t>
+          <t>333182</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>307098</t>
+          <t>333182</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -8008,17 +8008,17 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>294170</t>
+          <t>326243</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>294170</t>
+          <t>326243</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>294170</t>
+          <t>326243</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -8043,17 +8043,17 @@
       </c>
       <c r="R68" s="2" t="inlineStr">
         <is>
-          <t>601267</t>
+          <t>659425</t>
         </is>
       </c>
       <c r="S68" s="2" t="inlineStr">
         <is>
-          <t>601267</t>
+          <t>659425</t>
         </is>
       </c>
       <c r="T68" s="2" t="inlineStr">
         <is>
-          <t>601267</t>
+          <t>659425</t>
         </is>
       </c>
       <c r="U68" s="2" t="inlineStr">
@@ -8090,7 +8090,7 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>1472</t>
+          <t>1716</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>4487</t>
+          <t>6818</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -8125,7 +8125,7 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>1193</t>
+          <t>1322</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>4831</t>
+          <t>4643</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8160,32 +8160,32 @@
       </c>
       <c r="R69" s="2" t="inlineStr">
         <is>
-          <t>2665</t>
+          <t>3038</t>
         </is>
       </c>
       <c r="S69" s="2" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>845</t>
         </is>
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
-          <t>7191</t>
+          <t>7511</t>
         </is>
       </c>
       <c r="U69" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -8203,17 +8203,17 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>3148</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>749</t>
+          <t>993</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>7154</t>
+          <t>7688</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -8238,7 +8238,7 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>417</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>2420</t>
+          <t>1810</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8273,32 +8273,32 @@
       </c>
       <c r="R70" s="2" t="inlineStr">
         <is>
-          <t>3255</t>
+          <t>3566</t>
         </is>
       </c>
       <c r="S70" s="2" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>1109</t>
         </is>
       </c>
       <c r="T70" s="2" t="inlineStr">
         <is>
-          <t>7657</t>
+          <t>8723</t>
         </is>
       </c>
       <c r="U70" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -8655,32 +8655,32 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>756</t>
+          <t>816</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>6729</t>
+          <t>6994</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -8690,32 +8690,32 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>1803</t>
+          <t>2362</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>777</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>5346</t>
+          <t>5093</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -8725,32 +8725,32 @@
       </c>
       <c r="R74" s="2" t="inlineStr">
         <is>
-          <t>4252</t>
+          <t>4972</t>
         </is>
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>2411</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>9366</t>
+          <t>9988</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -8768,7 +8768,7 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>1743</t>
+          <t>1852</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -8778,12 +8778,12 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>5262</t>
+          <t>5601</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -8793,7 +8793,7 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
@@ -8803,32 +8803,32 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>2724</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>7116</t>
+          <t>5740</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -8838,32 +8838,32 @@
       </c>
       <c r="R75" s="2" t="inlineStr">
         <is>
-          <t>4383</t>
+          <t>4576</t>
         </is>
       </c>
       <c r="S75" s="2" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="T75" s="2" t="inlineStr">
         <is>
-          <t>9813</t>
+          <t>9467</t>
         </is>
       </c>
       <c r="U75" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -8881,32 +8881,32 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>6820</t>
+          <t>8174</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>3556</t>
+          <t>4013</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>13308</t>
+          <t>15025</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -8916,32 +8916,32 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>6067</t>
+          <t>6494</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>3648</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>14354</t>
+          <t>10438</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -8951,32 +8951,32 @@
       </c>
       <c r="R76" s="2" t="inlineStr">
         <is>
-          <t>12887</t>
+          <t>14668</t>
         </is>
       </c>
       <c r="S76" s="2" t="inlineStr">
         <is>
-          <t>4481</t>
+          <t>9247</t>
         </is>
       </c>
       <c r="T76" s="2" t="inlineStr">
         <is>
-          <t>22567</t>
+          <t>21582</t>
         </is>
       </c>
       <c r="U76" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -8994,22 +8994,22 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>3864</t>
+          <t>4304</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>1506</t>
+          <t>1643</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>8441</t>
+          <t>8676</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -9019,7 +9019,7 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
@@ -9029,32 +9029,32 @@
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>2620</t>
+          <t>3423</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>1544</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>7286</t>
+          <t>6828</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9064,32 +9064,32 @@
       </c>
       <c r="R77" s="2" t="inlineStr">
         <is>
-          <t>6484</t>
+          <t>7727</t>
         </is>
       </c>
       <c r="S77" s="2" t="inlineStr">
         <is>
-          <t>1761</t>
+          <t>4033</t>
         </is>
       </c>
       <c r="T77" s="2" t="inlineStr">
         <is>
-          <t>13115</t>
+          <t>13518</t>
         </is>
       </c>
       <c r="U77" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -9107,32 +9107,32 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>7621</t>
+          <t>8275</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>4298</t>
+          <t>4355</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>13247</t>
+          <t>14925</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
@@ -9142,32 +9142,32 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>6085</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>1371</t>
+          <t>3770</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>14634</t>
+          <t>11045</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -9177,32 +9177,32 @@
       </c>
       <c r="R78" s="2" t="inlineStr">
         <is>
-          <t>13706</t>
+          <t>15017</t>
         </is>
       </c>
       <c r="S78" s="2" t="inlineStr">
         <is>
-          <t>4362</t>
+          <t>9839</t>
         </is>
       </c>
       <c r="T78" s="2" t="inlineStr">
         <is>
-          <t>23829</t>
+          <t>21593</t>
         </is>
       </c>
       <c r="U78" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -9220,32 +9220,32 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>18898</t>
+          <t>20170</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>13345</t>
+          <t>14503</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>25238</t>
+          <t>27544</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
@@ -9255,32 +9255,32 @@
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>15970</t>
+          <t>17366</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>3972</t>
+          <t>12652</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>35804</t>
+          <t>23930</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -9290,32 +9290,32 @@
       </c>
       <c r="R79" s="2" t="inlineStr">
         <is>
-          <t>34868</t>
+          <t>37536</t>
         </is>
       </c>
       <c r="S79" s="2" t="inlineStr">
         <is>
-          <t>12871</t>
+          <t>29649</t>
         </is>
       </c>
       <c r="T79" s="2" t="inlineStr">
         <is>
-          <t>57536</t>
+          <t>46398</t>
         </is>
       </c>
       <c r="U79" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>10,65%</t>
         </is>
       </c>
     </row>
@@ -9333,32 +9333,32 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>148802</t>
+          <t>164478</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>139201</t>
+          <t>153161</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>158055</t>
+          <t>174126</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>76,6%</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>71,56%</t>
+          <t>71,33%</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -9368,32 +9368,32 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>368435</t>
+          <t>180238</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>326013</t>
+          <t>172119</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>394750</t>
+          <t>187532</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>81,52%</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>80,45%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -9403,32 +9403,32 @@
       </c>
       <c r="R80" s="2" t="inlineStr">
         <is>
-          <t>517237</t>
+          <t>344716</t>
         </is>
       </c>
       <c r="S80" s="2" t="inlineStr">
         <is>
-          <t>468985</t>
+          <t>330309</t>
         </is>
       </c>
       <c r="T80" s="2" t="inlineStr">
         <is>
-          <t>569161</t>
+          <t>357556</t>
         </is>
       </c>
       <c r="U80" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>79,1%</t>
         </is>
       </c>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>75,79%</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>82,04%</t>
         </is>
       </c>
     </row>
@@ -9446,17 +9446,17 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>194524</t>
+          <t>214727</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>194524</t>
+          <t>214727</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>194524</t>
+          <t>214727</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -9481,17 +9481,17 @@
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>405213</t>
+          <t>221088</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>405213</t>
+          <t>221088</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>405213</t>
+          <t>221088</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -9516,17 +9516,17 @@
       </c>
       <c r="R81" s="2" t="inlineStr">
         <is>
-          <t>599737</t>
+          <t>435815</t>
         </is>
       </c>
       <c r="S81" s="2" t="inlineStr">
         <is>
-          <t>599737</t>
+          <t>435815</t>
         </is>
       </c>
       <c r="T81" s="2" t="inlineStr">
         <is>
-          <t>599737</t>
+          <t>435815</t>
         </is>
       </c>
       <c r="U81" s="2" t="inlineStr">
@@ -9563,7 +9563,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>599</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -9573,12 +9573,12 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>3159</t>
+          <t>2976</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -9588,7 +9588,7 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>591</t>
+          <t>615</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
@@ -9608,12 +9608,12 @@
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>2934</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
@@ -9623,7 +9623,7 @@
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -9633,7 +9633,7 @@
       </c>
       <c r="R82" s="2" t="inlineStr">
         <is>
-          <t>1218</t>
+          <t>1214</t>
         </is>
       </c>
       <c r="S82" s="2" t="inlineStr">
@@ -9643,12 +9643,12 @@
       </c>
       <c r="T82" s="2" t="inlineStr">
         <is>
-          <t>4233</t>
+          <t>4212</t>
         </is>
       </c>
       <c r="U82" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="V82" s="2" t="inlineStr">
@@ -9658,7 +9658,7 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -9676,32 +9676,32 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>2259</t>
+          <t>2515</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>784</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>6073</t>
+          <t>6942</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
@@ -9711,32 +9711,32 @@
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>1581</t>
+          <t>1688</t>
         </is>
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>380</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>4665</t>
+          <t>4525</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -9746,32 +9746,32 @@
       </c>
       <c r="R83" s="2" t="inlineStr">
         <is>
-          <t>3839</t>
+          <t>4203</t>
         </is>
       </c>
       <c r="S83" s="2" t="inlineStr">
         <is>
-          <t>1415</t>
+          <t>1518</t>
         </is>
       </c>
       <c r="T83" s="2" t="inlineStr">
         <is>
-          <t>8447</t>
+          <t>8675</t>
         </is>
       </c>
       <c r="U83" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -10128,7 +10128,7 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>1523</t>
+          <t>1869</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>4704</t>
+          <t>5660</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -10153,7 +10153,7 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
@@ -10163,27 +10163,27 @@
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>1371</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>393</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>3963</t>
+          <t>4307</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10198,32 +10198,32 @@
       </c>
       <c r="R87" s="2" t="inlineStr">
         <is>
-          <t>2894</t>
+          <t>3318</t>
         </is>
       </c>
       <c r="S87" s="2" t="inlineStr">
         <is>
-          <t>992</t>
+          <t>1259</t>
         </is>
       </c>
       <c r="T87" s="2" t="inlineStr">
         <is>
-          <t>6475</t>
+          <t>8029</t>
         </is>
       </c>
       <c r="U87" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="V87" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -10241,7 +10241,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>1624</t>
+          <t>1587</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>5071</t>
+          <t>5094</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -10266,7 +10266,7 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
@@ -10276,7 +10276,7 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>1049</t>
+          <t>1084</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>4001</t>
+          <t>3945</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="O88" s="2" t="inlineStr">
@@ -10301,7 +10301,7 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -10311,32 +10311,32 @@
       </c>
       <c r="R88" s="2" t="inlineStr">
         <is>
-          <t>2673</t>
+          <t>2671</t>
         </is>
       </c>
       <c r="S88" s="2" t="inlineStr">
         <is>
-          <t>813</t>
+          <t>670</t>
         </is>
       </c>
       <c r="T88" s="2" t="inlineStr">
         <is>
-          <t>6883</t>
+          <t>7205</t>
         </is>
       </c>
       <c r="U88" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="V88" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -10354,32 +10354,32 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>3937</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>1551</t>
+          <t>2290</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>8895</t>
+          <t>10558</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
@@ -10389,67 +10389,67 @@
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>1190</t>
+          <t>1209</t>
         </is>
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>331</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>3497</t>
+          <t>3200</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
+          <t>1,25%</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R89" s="2" t="inlineStr">
+        <is>
+          <t>6209</t>
+        </is>
+      </c>
+      <c r="S89" s="2" t="inlineStr">
+        <is>
+          <t>2835</t>
+        </is>
+      </c>
+      <c r="T89" s="2" t="inlineStr">
+        <is>
+          <t>11762</t>
+        </is>
+      </c>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
           <t>1,48%</t>
         </is>
       </c>
-      <c r="Q89" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R89" s="2" t="inlineStr">
-        <is>
-          <t>5127</t>
-        </is>
-      </c>
-      <c r="S89" s="2" t="inlineStr">
-        <is>
-          <t>2258</t>
-        </is>
-      </c>
-      <c r="T89" s="2" t="inlineStr">
-        <is>
-          <t>9463</t>
-        </is>
-      </c>
-      <c r="U89" s="2" t="inlineStr">
-        <is>
-          <t>1,33%</t>
-        </is>
-      </c>
       <c r="V89" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -10467,32 +10467,32 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>2277</t>
+          <t>3003</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>744</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>5848</t>
+          <t>7361</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
@@ -10502,7 +10502,7 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>466</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
@@ -10512,12 +10512,12 @@
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>896</t>
+          <t>2343</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="O90" s="2" t="inlineStr">
@@ -10527,7 +10527,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -10537,32 +10537,32 @@
       </c>
       <c r="R90" s="2" t="inlineStr">
         <is>
-          <t>2441</t>
+          <t>3469</t>
         </is>
       </c>
       <c r="S90" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>1327</t>
         </is>
       </c>
       <c r="T90" s="2" t="inlineStr">
         <is>
-          <t>6546</t>
+          <t>8260</t>
         </is>
       </c>
       <c r="U90" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="V90" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -10580,32 +10580,32 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>5556</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>2487</t>
+          <t>2641</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>9698</t>
+          <t>10611</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
@@ -10615,32 +10615,32 @@
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>6849</t>
+          <t>7194</t>
         </is>
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>4033</t>
+          <t>4356</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>10681</t>
+          <t>11211</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -10650,32 +10650,32 @@
       </c>
       <c r="R91" s="2" t="inlineStr">
         <is>
-          <t>12155</t>
+          <t>12751</t>
         </is>
       </c>
       <c r="S91" s="2" t="inlineStr">
         <is>
-          <t>7726</t>
+          <t>8564</t>
         </is>
       </c>
       <c r="T91" s="2" t="inlineStr">
         <is>
-          <t>17395</t>
+          <t>18868</t>
         </is>
       </c>
       <c r="U91" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="V91" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -10693,32 +10693,32 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>15355</t>
+          <t>16645</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>10365</t>
+          <t>11496</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>22002</t>
+          <t>23274</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
@@ -10728,32 +10728,32 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>20633</t>
+          <t>22385</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>15298</t>
+          <t>16244</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>26752</t>
+          <t>29657</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -10763,32 +10763,32 @@
       </c>
       <c r="R92" s="2" t="inlineStr">
         <is>
-          <t>35988</t>
+          <t>39030</t>
         </is>
       </c>
       <c r="S92" s="2" t="inlineStr">
         <is>
-          <t>28850</t>
+          <t>30709</t>
         </is>
       </c>
       <c r="T92" s="2" t="inlineStr">
         <is>
-          <t>44427</t>
+          <t>48526</t>
         </is>
       </c>
       <c r="U92" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="V92" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,55%</t>
         </is>
       </c>
     </row>
@@ -10806,32 +10806,32 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>117115</t>
+          <t>127046</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>108570</t>
+          <t>117643</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>125108</t>
+          <t>134932</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>77,55%</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
@@ -10841,32 +10841,32 @@
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>202976</t>
+          <t>220127</t>
         </is>
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>195584</t>
+          <t>210896</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>209893</t>
+          <t>227399</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>82,31%</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -10876,32 +10876,32 @@
       </c>
       <c r="R93" s="2" t="inlineStr">
         <is>
-          <t>320091</t>
+          <t>347173</t>
         </is>
       </c>
       <c r="S93" s="2" t="inlineStr">
         <is>
-          <t>309123</t>
+          <t>334173</t>
         </is>
       </c>
       <c r="T93" s="2" t="inlineStr">
         <is>
-          <t>330621</t>
+          <t>358251</t>
         </is>
       </c>
       <c r="U93" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="V93" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>79,56%</t>
         </is>
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>85,29%</t>
         </is>
       </c>
     </row>
@@ -10919,17 +10919,17 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>150023</t>
+          <t>163820</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>150023</t>
+          <t>163820</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>150023</t>
+          <t>163820</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -10954,17 +10954,17 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>236404</t>
+          <t>256218</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>236404</t>
+          <t>256218</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>236404</t>
+          <t>256218</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -10989,17 +10989,17 @@
       </c>
       <c r="R94" s="2" t="inlineStr">
         <is>
-          <t>386427</t>
+          <t>420038</t>
         </is>
       </c>
       <c r="S94" s="2" t="inlineStr">
         <is>
-          <t>386427</t>
+          <t>420038</t>
         </is>
       </c>
       <c r="T94" s="2" t="inlineStr">
         <is>
-          <t>386427</t>
+          <t>420038</t>
         </is>
       </c>
       <c r="U94" s="2" t="inlineStr">
@@ -11036,102 +11036,102 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>11657</t>
+          <t>13306</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>5700</t>
+          <t>6638</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>20482</t>
+          <t>23549</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>12294</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>6787</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>23261</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>1,25%</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="R95" s="2" t="inlineStr">
+        <is>
+          <t>25600</t>
+        </is>
+      </c>
+      <c r="S95" s="2" t="inlineStr">
+        <is>
+          <t>17012</t>
+        </is>
+      </c>
+      <c r="T95" s="2" t="inlineStr">
+        <is>
+          <t>39584</t>
+        </is>
+      </c>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
           <t>0,7%</t>
         </is>
       </c>
-      <c r="H95" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="I95" s="2" t="inlineStr">
-        <is>
-          <t>1,24%</t>
-        </is>
-      </c>
-      <c r="J95" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K95" s="2" t="inlineStr">
-        <is>
-          <t>11310</t>
-        </is>
-      </c>
-      <c r="L95" s="2" t="inlineStr">
-        <is>
-          <t>5623</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr">
-        <is>
-          <t>21812</t>
-        </is>
-      </c>
-      <c r="N95" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="O95" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="P95" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="Q95" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="R95" s="2" t="inlineStr">
-        <is>
-          <t>22967</t>
-        </is>
-      </c>
-      <c r="S95" s="2" t="inlineStr">
-        <is>
-          <t>14626</t>
-        </is>
-      </c>
-      <c r="T95" s="2" t="inlineStr">
-        <is>
-          <t>34500</t>
-        </is>
-      </c>
-      <c r="U95" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
       <c r="V95" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -11149,32 +11149,32 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>23657</t>
+          <t>25864</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>14063</t>
+          <t>16258</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>39894</t>
+          <t>42946</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
@@ -11184,32 +11184,32 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>15035</t>
+          <t>17446</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>8986</t>
+          <t>10930</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>23820</t>
+          <t>27717</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -11219,32 +11219,32 @@
       </c>
       <c r="R96" s="2" t="inlineStr">
         <is>
-          <t>38691</t>
+          <t>43311</t>
         </is>
       </c>
       <c r="S96" s="2" t="inlineStr">
         <is>
-          <t>26686</t>
+          <t>31420</t>
         </is>
       </c>
       <c r="T96" s="2" t="inlineStr">
         <is>
-          <t>60935</t>
+          <t>63188</t>
         </is>
       </c>
       <c r="U96" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="V96" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -11297,7 +11297,7 @@
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>715</t>
         </is>
       </c>
       <c r="L97" s="2" t="inlineStr">
@@ -11307,12 +11307,12 @@
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>3025</t>
+          <t>4663</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="O97" s="2" t="inlineStr">
@@ -11322,7 +11322,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -11332,7 +11332,7 @@
       </c>
       <c r="R97" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>715</t>
         </is>
       </c>
       <c r="S97" s="2" t="inlineStr">
@@ -11342,7 +11342,7 @@
       </c>
       <c r="T97" s="2" t="inlineStr">
         <is>
-          <t>3409</t>
+          <t>3510</t>
         </is>
       </c>
       <c r="U97" s="2" t="inlineStr">
@@ -11375,32 +11375,32 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>2619</t>
+          <t>4952</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>1464</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>9393</t>
+          <t>12374</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
@@ -11410,32 +11410,32 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>4339</t>
+          <t>3979</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>1194</t>
+          <t>1388</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>11269</t>
+          <t>10099</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
@@ -11445,32 +11445,32 @@
       </c>
       <c r="R98" s="2" t="inlineStr">
         <is>
-          <t>6958</t>
+          <t>8931</t>
         </is>
       </c>
       <c r="S98" s="2" t="inlineStr">
         <is>
-          <t>2988</t>
+          <t>4162</t>
         </is>
       </c>
       <c r="T98" s="2" t="inlineStr">
         <is>
-          <t>14177</t>
+          <t>16872</t>
         </is>
       </c>
       <c r="U98" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="V98" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,46%</t>
         </is>
       </c>
     </row>
@@ -11523,27 +11523,27 @@
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>3950</t>
+          <t>4047</t>
         </is>
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>1256</t>
+          <t>1454</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>8808</t>
+          <t>8501</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -11558,17 +11558,17 @@
       </c>
       <c r="R99" s="2" t="inlineStr">
         <is>
-          <t>3950</t>
+          <t>4047</t>
         </is>
       </c>
       <c r="S99" s="2" t="inlineStr">
         <is>
-          <t>1406</t>
+          <t>1498</t>
         </is>
       </c>
       <c r="T99" s="2" t="inlineStr">
         <is>
-          <t>9455</t>
+          <t>9079</t>
         </is>
       </c>
       <c r="U99" s="2" t="inlineStr">
@@ -11583,7 +11583,7 @@
       </c>
       <c r="W99" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,25%</t>
         </is>
       </c>
     </row>
@@ -11601,32 +11601,32 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>18628</t>
+          <t>19827</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>11562</t>
+          <t>11960</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>30913</t>
+          <t>30820</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
@@ -11636,32 +11636,32 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>18878</t>
+          <t>20531</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>12209</t>
+          <t>13852</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>27779</t>
+          <t>29429</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr">
@@ -11671,32 +11671,32 @@
       </c>
       <c r="R100" s="2" t="inlineStr">
         <is>
-          <t>37506</t>
+          <t>40358</t>
         </is>
       </c>
       <c r="S100" s="2" t="inlineStr">
         <is>
-          <t>26150</t>
+          <t>29655</t>
         </is>
       </c>
       <c r="T100" s="2" t="inlineStr">
         <is>
-          <t>50470</t>
+          <t>53727</t>
         </is>
       </c>
       <c r="U100" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="V100" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -11714,97 +11714,97 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>10461</t>
+          <t>10347</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>4745</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>18808</t>
+          <t>18180</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>1,01%</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>12601</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>7718</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>19903</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>0,68%</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="R101" s="2" t="inlineStr">
+        <is>
+          <t>22948</t>
+        </is>
+      </c>
+      <c r="S101" s="2" t="inlineStr">
+        <is>
+          <t>15606</t>
+        </is>
+      </c>
+      <c r="T101" s="2" t="inlineStr">
+        <is>
+          <t>34242</t>
+        </is>
+      </c>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
           <t>0,63%</t>
         </is>
       </c>
-      <c r="H101" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="I101" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="J101" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K101" s="2" t="inlineStr">
-        <is>
-          <t>12249</t>
-        </is>
-      </c>
-      <c r="L101" s="2" t="inlineStr">
-        <is>
-          <t>7078</t>
-        </is>
-      </c>
-      <c r="M101" s="2" t="inlineStr">
-        <is>
-          <t>19382</t>
-        </is>
-      </c>
-      <c r="N101" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="O101" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="P101" s="2" t="inlineStr">
-        <is>
-          <t>1,02%</t>
-        </is>
-      </c>
-      <c r="Q101" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="R101" s="2" t="inlineStr">
-        <is>
-          <t>22709</t>
-        </is>
-      </c>
-      <c r="S101" s="2" t="inlineStr">
-        <is>
-          <t>14534</t>
-        </is>
-      </c>
-      <c r="T101" s="2" t="inlineStr">
-        <is>
-          <t>33329</t>
-        </is>
-      </c>
-      <c r="U101" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
       <c r="V101" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W101" s="2" t="inlineStr">
@@ -11827,32 +11827,32 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>42270</t>
+          <t>46656</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>27483</t>
+          <t>32865</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>66248</t>
+          <t>69958</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
@@ -11862,32 +11862,32 @@
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>78670</t>
+          <t>51646</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>39148</t>
+          <t>39650</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>193213</t>
+          <t>67758</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr">
@@ -11897,32 +11897,32 @@
       </c>
       <c r="R102" s="2" t="inlineStr">
         <is>
-          <t>120940</t>
+          <t>98302</t>
         </is>
       </c>
       <c r="S102" s="2" t="inlineStr">
         <is>
-          <t>79237</t>
+          <t>77732</t>
         </is>
       </c>
       <c r="T102" s="2" t="inlineStr">
         <is>
-          <t>258990</t>
+          <t>127040</t>
         </is>
       </c>
       <c r="U102" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="V102" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W102" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -11940,32 +11940,32 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>36755</t>
+          <t>37958</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>25010</t>
+          <t>26536</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>52351</t>
+          <t>55974</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
@@ -11975,32 +11975,32 @@
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>18958</t>
+          <t>21671</t>
         </is>
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>11516</t>
+          <t>14929</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>28036</t>
+          <t>30193</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -12010,32 +12010,32 @@
       </c>
       <c r="R103" s="2" t="inlineStr">
         <is>
-          <t>55713</t>
+          <t>59629</t>
         </is>
       </c>
       <c r="S103" s="2" t="inlineStr">
         <is>
-          <t>41144</t>
+          <t>45096</t>
         </is>
       </c>
       <c r="T103" s="2" t="inlineStr">
         <is>
-          <t>72978</t>
+          <t>77475</t>
         </is>
       </c>
       <c r="U103" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="V103" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W103" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -12053,32 +12053,32 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>100839</t>
+          <t>106492</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>77744</t>
+          <t>82904</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>131878</t>
+          <t>134298</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
@@ -12088,32 +12088,32 @@
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>80479</t>
+          <t>92052</t>
         </is>
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>57592</t>
+          <t>78101</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>99232</t>
+          <t>110705</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
@@ -12123,32 +12123,32 @@
       </c>
       <c r="R104" s="2" t="inlineStr">
         <is>
-          <t>181318</t>
+          <t>198544</t>
         </is>
       </c>
       <c r="S104" s="2" t="inlineStr">
         <is>
-          <t>142242</t>
+          <t>171018</t>
         </is>
       </c>
       <c r="T104" s="2" t="inlineStr">
         <is>
-          <t>220409</t>
+          <t>229259</t>
         </is>
       </c>
       <c r="U104" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="V104" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W104" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -12166,32 +12166,32 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>190204</t>
+          <t>204442</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>166850</t>
+          <t>177455</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>218082</t>
+          <t>229810</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
@@ -12201,32 +12201,32 @@
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>178265</t>
+          <t>193335</t>
         </is>
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>122472</t>
+          <t>171171</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>209894</t>
+          <t>217738</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="Q105" s="2" t="inlineStr">
@@ -12236,32 +12236,32 @@
       </c>
       <c r="R105" s="2" t="inlineStr">
         <is>
-          <t>368470</t>
+          <t>397778</t>
         </is>
       </c>
       <c r="S105" s="2" t="inlineStr">
         <is>
-          <t>300886</t>
+          <t>364134</t>
         </is>
       </c>
       <c r="T105" s="2" t="inlineStr">
         <is>
-          <t>410475</t>
+          <t>436288</t>
         </is>
       </c>
       <c r="U105" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="V105" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="W105" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,93%</t>
         </is>
       </c>
     </row>
@@ -12279,32 +12279,32 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>1217946</t>
+          <t>1331230</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>1172583</t>
+          <t>1284265</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>1257039</t>
+          <t>1369981</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>73,91%</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>71,31%</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
@@ -12314,32 +12314,32 @@
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>1485002</t>
+          <t>1426164</t>
         </is>
       </c>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>1405072</t>
+          <t>1391742</t>
         </is>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>1605310</t>
+          <t>1458383</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>76,82%</t>
         </is>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>73,65%</t>
+          <t>74,97%</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="Q106" s="2" t="inlineStr">
@@ -12349,32 +12349,32 @@
       </c>
       <c r="R106" s="2" t="inlineStr">
         <is>
-          <t>2702949</t>
+          <t>2757393</t>
         </is>
       </c>
       <c r="S106" s="2" t="inlineStr">
         <is>
-          <t>2615583</t>
+          <t>2704879</t>
         </is>
       </c>
       <c r="T106" s="2" t="inlineStr">
         <is>
-          <t>2854479</t>
+          <t>2809037</t>
         </is>
       </c>
       <c r="U106" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>75,39%</t>
         </is>
       </c>
       <c r="V106" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>73,95%</t>
         </is>
       </c>
       <c r="W106" s="2" t="inlineStr">
         <is>
-          <t>80,12%</t>
+          <t>76,8%</t>
         </is>
       </c>
     </row>
@@ -12392,17 +12392,17 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>1655035</t>
+          <t>1801075</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>1655035</t>
+          <t>1801075</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>1655035</t>
+          <t>1801075</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -12427,17 +12427,17 @@
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>1907795</t>
+          <t>1856481</t>
         </is>
       </c>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>1907795</t>
+          <t>1856481</t>
         </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>1907795</t>
+          <t>1856481</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
@@ -12462,17 +12462,17 @@
       </c>
       <c r="R107" s="2" t="inlineStr">
         <is>
-          <t>3562831</t>
+          <t>3657555</t>
         </is>
       </c>
       <c r="S107" s="2" t="inlineStr">
         <is>
-          <t>3562831</t>
+          <t>3657555</t>
         </is>
       </c>
       <c r="T107" s="2" t="inlineStr">
         <is>
-          <t>3562831</t>
+          <t>3657555</t>
         </is>
       </c>
       <c r="U107" s="2" t="inlineStr">

--- a/data/trans_orig/AIRE_1-Edad-trans_orig.xlsx
+++ b/data/trans_orig/AIRE_1-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según lo que estarían dispuestos a pagar al año para que la administración pública ponga en marcha actuaciones (+++) en su municipio/ciudad (o lugar de residencia) que haga reducir la contaminación del aire en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Población según lo que estaría dispuesta a pagar al año para que la administración pública ponga en marcha actuaciones en su municipio/ciudad (o lugar de residencia) que haga reducir la contaminación del aire en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
